--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00842B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00842B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9481F78-E177-4257-ADEE-44E6B43E01FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E49CADC8-4521-4F03-AA10-EB77C2C4437D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6B81997B-AA9E-4801-8656-F7B11A87D5C6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D9BE8F8B-7D2C-42ED-B67D-1326DA3EEB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="00842B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1594,20 +1594,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490007BE-1E5A-448E-888E-E944382D623C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7789FB-D5F9-4D51-A11C-6D4BBF4FF37E}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1761,7 +1761,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1841,7 +1841,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
         <v>69</v>
       </c>
